--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="path_manager" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="database" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1709,6 +1715,114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>函数名/类名</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>queryEmails</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>db&lt;MailDatabase&gt;; category&lt;str|None&gt;; condition&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>list&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>按条件查询邮件(主题/收件人/发件人/日期范围)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(src/activity/mail_query.py)[queryEmails:19]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2190,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7138,7 +7252,6 @@
         </is>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -7477,7 +7590,6 @@
         </is>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -7520,7 +7632,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
@@ -7563,7 +7674,6 @@
         </is>
       </c>
     </row>
-    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -7601,7 +7711,6 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
@@ -7644,7 +7753,6 @@
         </is>
       </c>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -7687,7 +7795,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -7730,7 +7837,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
@@ -7773,7 +7879,6 @@
         </is>
       </c>
     </row>
-    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -7813,6 +7918,505 @@
       <c r="H156" t="inlineStr">
         <is>
           <t>新增(替代旧占位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RecipientPickerDialog</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>收件人选择器(群发):选收件人Excel/TXT并勾选,UI占位</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog:1156]</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>onPickFile</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>弹文件对话框选xlsx/xls/txt后解析并展示(解析占位)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;onPickFile:1230]</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>_loadRecipientsFromFile</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>从文件读收件人(占位,待接入解析API)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_loadRecipientsFromFile:1244]</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>setRecipients</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>recipients&lt;list&lt;str&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>用收件人列表填充可勾选列表(默认全选)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;setRecipients:1256]</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>_addRecipientItem</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>item&lt;QListWidgetItem&gt;</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>把单个收件人条目加入列表</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_addRecipientItem:1275]</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>_onItemToggled</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>_item</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>列表勾选变化时刷新计数</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_onItemToggled:1281]</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>_setAllChecked</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>checked&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>全选或取消全选</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_setAllChecked:1285]</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>_checkedRecipients</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>返回当前勾选收件人</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_checkedRecipients:1296]</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>getSelectedRecipients</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>供外部读取确定后勾选的收件人</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;getSelectedRecipients:1304]</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>_updateCount</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>刷新已勾选/共计数文案</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_updateCount:1312]</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>_updateButtons</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>按列表是否为空启用/禁用全选清空按钮</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_updateButtons:1318]</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>onPickRecipients</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>打开收件人选择器,确定后合并回填收件人框</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;onPickRecipients:1592]</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:37:50</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8869,7 +9473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9543,7 +10147,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -9586,7 +10189,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -9624,7 +10226,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -9662,6 +10263,408 @@
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>函数名/类名</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>isValidEmail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>判断字符串是否合法邮箱地址</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[isValidEmail:21]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>parseRecipientFile</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>从Excel(.xlsx/.xls)或TXT读取识别收件人邮箱(去重)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[parseRecipientFile:34]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>_parseTxt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>解析TXT逐行识别邮箱</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_parseTxt:58]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>_parseExcel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>按扩展名分发解析Excel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_parseExcel:72]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>_parseXlsx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>用openpyxl读取xlsx工作表识别邮箱</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_parseXlsx:87]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>_parseXls</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>用xlrd读取旧版xls识别邮箱</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_parseXls:105]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>_dedupKeepOrder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>items&lt;list&lt;str&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>列表去重保持首次顺序</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_dedupKeepOrder:130]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mergeRecipients</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>current_text&lt;str&gt;; selected&lt;list&lt;str&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>合并已有+新增收件人(去重滤空,分号分隔)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[mergeRecipients:143]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:51:33</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>新增</t>
         </is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -10279,7 +10279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10357,22 +10357,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>判断字符串是否合法邮箱地址</t>
+          <t>判断字符串是否完全等于一个合法邮箱</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(src/activity/recipient_bulk.py)[isValidEmail:21]</t>
+          <t>(src/activity/recipient_bulk.py)[isValidEmail:19]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-23 20:51:33</t>
+          <t>2026-08-23 20:57:59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>改用EMAIL_FIND_RE.fullmatch</t>
         </is>
       </c>
     </row>
@@ -10399,22 +10399,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>从Excel(.xlsx/.xls)或TXT读取识别收件人邮箱(去重)</t>
+          <t>从Excel/TXT读取识别收件人邮箱(去重)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(src/activity/recipient_bulk.py)[parseRecipientFile:34]</t>
+          <t>(src/activity/recipient_bulk.py)[parseRecipientFile:53]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-23 20:51:33</t>
+          <t>2026-08-23 20:57:59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>增强提取逻辑</t>
         </is>
       </c>
     </row>
@@ -10441,22 +10441,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>解析TXT逐行识别邮箱</t>
+          <t>TXT逐行提取邮箱(支持一行多邮箱分隔)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(src/activity/recipient_bulk.py)[_parseTxt:58]</t>
+          <t>(src/activity/recipient_bulk.py)[_parseTxt:78]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-23 20:51:33</t>
+          <t>2026-08-23 20:57:59</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>增强</t>
         </is>
       </c>
     </row>
@@ -10525,22 +10525,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>用openpyxl读取xlsx工作表识别邮箱</t>
+          <t>openpyxl读xlsx首表单元格提取邮箱</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(src/activity/recipient_bulk.py)[_parseXlsx:87]</t>
+          <t>(src/activity/recipient_bulk.py)[_parseXlsx:114]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-23 20:51:33</t>
+          <t>2026-08-23 20:57:59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>增强</t>
         </is>
       </c>
     </row>
@@ -10567,22 +10567,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>用xlrd读取旧版xls识别邮箱</t>
+          <t>xlrd读旧版xls提取邮箱</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(src/activity/recipient_bulk.py)[_parseXls:105]</t>
+          <t>(src/activity/recipient_bulk.py)[_parseXls:139]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-23 20:51:33</t>
+          <t>2026-08-23 20:57:59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>增强</t>
         </is>
       </c>
     </row>
@@ -10665,6 +10665,48 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>extractEmails</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>从任意文本提取所有邮箱(支持一格多邮箱)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[extractEmails:31]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:57:59</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>新增</t>
         </is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MainEmail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="runTest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIRunTest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MainGUI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NormalMode" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="path_manager" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="database" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MainEmail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="runTest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GUIRunTest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MainGUI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NormalMode" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="main" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="path_manager" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="database" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7252,6 +7252,7 @@
         </is>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -7590,6 +7591,7 @@
         </is>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -7632,6 +7634,7 @@
         </is>
       </c>
     </row>
+    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
@@ -7674,6 +7677,7 @@
         </is>
       </c>
     </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -7711,6 +7715,7 @@
         </is>
       </c>
     </row>
+    <row r="147"/>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
@@ -7753,6 +7758,7 @@
         </is>
       </c>
     </row>
+    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -7795,6 +7801,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -7837,6 +7844,7 @@
         </is>
       </c>
     </row>
+    <row r="153"/>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
@@ -7879,6 +7887,7 @@
         </is>
       </c>
     </row>
+    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -7921,6 +7930,7 @@
         </is>
       </c>
     </row>
+    <row r="157"/>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
@@ -7958,6 +7968,7 @@
         </is>
       </c>
     </row>
+    <row r="159"/>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
@@ -7991,15 +8002,16 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-08-23 20:37:50</t>
+          <t>2026-08-23 21:07:41</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
+          <t>异常兜底扩展为(ValueError,ImportError),修复Excel闪退</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -8042,6 +8054,7 @@
         </is>
       </c>
     </row>
+    <row r="163"/>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
@@ -8084,6 +8097,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
@@ -8126,6 +8140,7 @@
         </is>
       </c>
     </row>
+    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -8168,6 +8183,7 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
@@ -8210,6 +8226,7 @@
         </is>
       </c>
     </row>
+    <row r="171"/>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -8252,6 +8269,7 @@
         </is>
       </c>
     </row>
+    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
@@ -8294,6 +8312,7 @@
         </is>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
@@ -8336,6 +8355,7 @@
         </is>
       </c>
     </row>
+    <row r="177"/>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
@@ -8378,6 +8398,7 @@
         </is>
       </c>
     </row>
+    <row r="179"/>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7959,12 +7959,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-08-23 20:37:50</t>
+          <t>2026-08-23 21:13:49</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>新增排序搜索</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-08-23 21:07:41</t>
+          <t>2026-08-23 21:13:49</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>异常兜底扩展为(ValueError,ImportError),修复Excel闪退</t>
+          <t>无代码变更</t>
         </is>
       </c>
     </row>
@@ -8088,12 +8088,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-08-23 20:37:50</t>
+          <t>2026-08-23 21:13:49</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>修改:状态管理</t>
         </is>
       </c>
     </row>
@@ -8438,6 +8438,216 @@
       <c r="H180" t="inlineStr">
         <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>_setComboSilent</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>index&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>不触发回调地切换排序下拉</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_setComboSilent:1302]</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>_onSortChanged</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>index&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>排序变更后重渲染列表</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_onSortChanged:1314]</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>_onSearchChanged</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>搜索文本变更后按关键字重渲染</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_onSearchChanged:1319]</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>_renderList</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>按排序+搜索重渲染列表且保留勾选</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientPickerDialog-&gt;_renderList:1323]</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>mergeRecipients</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>(import)合并收件人</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;onPickRecipients]</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>现由activity提供</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10733,6 +10943,132 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>函数名/类名</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sortRecipients</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>emails&lt;list&lt;str&gt;&gt;; by_letter&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>按首字母(A-Z不分大小写)排序或不排序</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[sortRecipients:193]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>filterRecipients</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>emails&lt;list&lt;str&gt;&gt;; keyword&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>筛选出包含关键字的邮箱(忽略大小写)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[filterRecipients:208]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:13:49</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -7252,7 +7252,6 @@
         </is>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -7591,7 +7590,6 @@
         </is>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -7634,7 +7632,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
@@ -7677,7 +7674,6 @@
         </is>
       </c>
     </row>
-    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -7715,7 +7711,6 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
@@ -7758,7 +7753,6 @@
         </is>
       </c>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -7801,7 +7795,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -7844,7 +7837,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
@@ -7887,7 +7879,6 @@
         </is>
       </c>
     </row>
-    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -7930,7 +7921,6 @@
         </is>
       </c>
     </row>
-    <row r="157"/>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
@@ -7968,7 +7958,6 @@
         </is>
       </c>
     </row>
-    <row r="159"/>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
@@ -8011,7 +8000,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -8054,7 +8042,6 @@
         </is>
       </c>
     </row>
-    <row r="163"/>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
@@ -8097,7 +8084,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
@@ -8140,7 +8126,6 @@
         </is>
       </c>
     </row>
-    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -8183,7 +8168,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
@@ -8226,7 +8210,6 @@
         </is>
       </c>
     </row>
-    <row r="171"/>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -8269,7 +8252,6 @@
         </is>
       </c>
     </row>
-    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
@@ -8312,7 +8294,6 @@
         </is>
       </c>
     </row>
-    <row r="175"/>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
@@ -8355,7 +8336,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
@@ -8398,7 +8378,6 @@
         </is>
       </c>
     </row>
-    <row r="179"/>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
@@ -10510,7 +10489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10640,12 +10619,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-23 20:57:59</t>
+          <t>2026-08-23 23:05:19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>增强提取逻辑</t>
+          <t>新增支持csv,提示文案更新</t>
         </is>
       </c>
     </row>
@@ -10682,12 +10661,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-23 20:57:59</t>
+          <t>2026-08-23 23:05:19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>增强</t>
+          <t>csv复用同一逻辑</t>
         </is>
       </c>
     </row>
@@ -10766,12 +10745,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-23 20:57:59</t>
+          <t>2026-08-23 23:05:19</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>增强</t>
+          <t>遍历所有sheet</t>
         </is>
       </c>
     </row>
@@ -10808,12 +10787,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-23 20:57:59</t>
+          <t>2026-08-23 23:05:19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>增强</t>
+          <t>遍历所有sheet</t>
         </is>
       </c>
     </row>
@@ -11066,6 +11045,48 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>函数名/类名</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>其他</t>
         </is>
       </c>
     </row>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7252,6 +7252,7 @@
         </is>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -7590,6 +7591,7 @@
         </is>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -7632,6 +7634,7 @@
         </is>
       </c>
     </row>
+    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
@@ -7674,6 +7677,7 @@
         </is>
       </c>
     </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -7711,6 +7715,7 @@
         </is>
       </c>
     </row>
+    <row r="147"/>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
@@ -7753,6 +7758,7 @@
         </is>
       </c>
     </row>
+    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -7795,6 +7801,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -7837,6 +7844,7 @@
         </is>
       </c>
     </row>
+    <row r="153"/>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
@@ -7879,6 +7887,7 @@
         </is>
       </c>
     </row>
+    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -7921,6 +7930,7 @@
         </is>
       </c>
     </row>
+    <row r="157"/>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
@@ -7958,6 +7968,7 @@
         </is>
       </c>
     </row>
+    <row r="159"/>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
@@ -8000,6 +8011,7 @@
         </is>
       </c>
     </row>
+    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -8042,6 +8054,7 @@
         </is>
       </c>
     </row>
+    <row r="163"/>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
@@ -8084,6 +8097,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
@@ -8126,6 +8140,7 @@
         </is>
       </c>
     </row>
+    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -8168,6 +8183,7 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
@@ -8210,6 +8226,7 @@
         </is>
       </c>
     </row>
+    <row r="171"/>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -8252,6 +8269,7 @@
         </is>
       </c>
     </row>
+    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
@@ -8294,6 +8312,7 @@
         </is>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
@@ -8336,6 +8355,7 @@
         </is>
       </c>
     </row>
+    <row r="177"/>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
@@ -8378,6 +8398,7 @@
         </is>
       </c>
     </row>
+    <row r="179"/>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
@@ -8627,6 +8648,300 @@
       <c r="H185" t="inlineStr">
         <is>
           <t>现由activity提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>RecipientManageDialog</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>parent&lt;QWidget|None&gt;</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>查看管理所有收件人:排序/搜索/勾选/非法标红</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientManageDialog:1409]</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>RecipientManageDialog-&gt;loadFromText</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>从输入框文本载入收件人并标记非法项</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientManageDialog-&gt;loadFromText:1494]</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>RecipientManageDialog-&gt;_renderList</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>按排序+搜索重渲染列表(非法标红)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientManageDialog-&gt;_renderList:1516]</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>RecipientManageDialog-&gt;getCheckedText</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>返回回写输入框的拼接文本</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientManageDialog-&gt;getCheckedText:1564]</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>RecipientManageDialog-&gt;hasInvalid</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>返回非法邮箱片段列表</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[RecipientManageDialog-&gt;hasInvalid:1573]</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>NormalPage-&gt;onManageRecipients</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>打开查看所有收件人对话框并回写输入框(含非法提示)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;onManageRecipients:1885]</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NormalPage-&gt;buildRecipientArea</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>构建收件人区(新增查看所有收件人按钮)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;buildRecipientArea:1759]</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>增加按钮</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11090,6 +11405,132 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>函数名/类名</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>splitRecipients</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>按分隔符拆分输入框文本为片段列表</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[splitRecipients:178]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>validateRecipients</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>tokens&lt;list&lt;str&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>tuple</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>校验片段区分合法/非法</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[validateRecipients:195]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:14:16</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8942,6 +8942,342 @@
       <c r="H192" t="inlineStr">
         <is>
           <t>增加按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>AdvancedPage</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>db&lt;MailDatabase&gt;, on_back&lt;callable&gt;</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>高级模式发信页，支持变量标记</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage:714]</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_buildUi</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>构建高级模式页面布局</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildUi:740]</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_buildTopBar</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>QHBoxLayout</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>构建顶部操作栏</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildTopBar:828]</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_markSelectionAsVariable</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>widget&lt;QLineEdit|QTextEdit&gt;</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>将选中文字标记为变量</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_markSelectionAsVariable:853]</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_removeVariableAtCursor</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>widget&lt;QLineEdit|QTextEdit&gt;</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>删除光标处的变量标记</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_removeVariableAtCursor:887]</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_findVariableAround</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;, pos&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>re.Match|None</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>查找光标位置附近的变量匹配</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_findVariableAround:914]</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_clearAllVariables</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>清空所有变量标记</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_clearAllVariables:930]</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_updateVariableList</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>解析并更新变量列表</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_updateVariableList:936]</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:00:13</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:10:38</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>重构:继承NormalPage,复用所有功能</t>
         </is>
       </c>
     </row>
@@ -9276,6 +9276,216 @@
         </is>
       </c>
       <c r="H200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_buildAdvancedUi</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>在普通模式UI基础上添加高级模式特有功能</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildAdvancedUi:747]</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:10:38</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>重构</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_enhanceSubjectEditor</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>为主题编辑器添加变量标记按钮</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_enhanceSubjectEditor:764]</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:10:38</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>重构</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_enhanceBodyEditor</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>为正文编辑器添加变量标记功能</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_enhanceBodyEditor:788]</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:10:38</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>重构</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_addDataImportButton</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>在顶部操作栏添加数据导入按钮</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_addDataImportButton:844]</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:10:38</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_onImportData</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>导入数据文件(UI占位)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onImportData:947]</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:10:38</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t>新增</t>
         </is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I205"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-08-24 12:10:38</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>重构:继承NormalPage,复用所有功能</t>
+          <t>新增/改为继承NormalPage</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:13</t>
+          <t>2026-08-24 12:31:02</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9486,6 +9486,48 @@
         </is>
       </c>
       <c r="H205" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;buildUi</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>构建高级模式布局：左=完整写信编辑区,右=变量标记面板</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;buildUi:2747]</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:31:02</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
         <is>
           <t>新增</t>
         </is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MainEmail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="runTest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GUIRunTest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MainGUI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NormalMode" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="main" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="path_manager" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="database" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MainEmail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="runTest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIRunTest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MainGUI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NormalMode" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="path_manager" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="database" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2720,12 +2720,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;buildUi:145]</t>
+          <t>2026-08-24 14:29:46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-08-23 11:34:16</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3021,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[NormalPage-&gt;buildTitleRow:392]</t>
+          <t>2026-08-24 15:39:35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026-08-23 11:34:16</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>主题输入框改用MarkableLineEdit以支持变量段局部高亮</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5422,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[ComposeModePage-&gt;buildUi:393]</t>
+          <t>2026-08-24 14:29:46</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>2026-08-23 15:47:11</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5548,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;buildUi:479]</t>
+          <t>2026-08-24 14:29:46</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>2026-08-23 15:47:11</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
         </is>
       </c>
     </row>
@@ -9015,7 +9035,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildUi:740]</t>
+          <t>2026-08-24 14:29:46</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -9025,7 +9045,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9119,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_markSelectionAsVariable:853]</t>
+          <t>2026-08-24 14:24:14</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -9109,7 +9129,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>修复：正文失焦后恢复选区委据，正确包裹选中文字并加背景高亮</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9161,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_removeVariableAtCursor:887]</t>
+          <t>2026-08-24 14:05:50</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -9151,7 +9171,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>更新：删除变量时同步清除背景高亮格式</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9539,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;buildUi:2747]</t>
+          <t>2026-08-24 14:29:46</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9529,7 +9549,3324 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_markVariableFromPanel</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>从右侧面板统一触发变量标记,自动判定目标输入框(主题/正文)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_markVariableFromPanel:2853]</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:38:49</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_targetVariableWidget</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>QLineEdit|QTextEdit</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>返回应作用的目标输入框:优先含选中文字者,其次获焦输入框,默认正文编辑器</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:15:18</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:38:49</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>更新：引入 _last_selected_widget 机制，解决 QLineEdit 失焦后选中状态丢失问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;buildUi</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>重写为高级模式配置页(四步向导第1步):左侧分区布局+右侧变量面板+底部下一步</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:29:46</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>优化布局:正文上移更高(最小高度300),附件下移更矮(列表高度60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_makeSection</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>title&lt;str&gt;, hint&lt;str&gt;, content_factory&lt;callable&gt;</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>QFrame</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>生成分组视觉区块:标题+提示+内容区</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_makeSection:2871]</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>新增(配置页子构件)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;buildStepIndicator</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>current_step&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>构建四步向导进度指示器(配置/负载/预览/发信)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;buildStepIndicator:2895]</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;buildStepFooter</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>QHBoxLayout</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>构建底部导航条:上一步(第1步禁用)+下一步</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;buildStepFooter:2925]</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_buildVariablePanel</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>构建右侧变量标记面板(蓝色标记按钮+变量列表+清空)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildVariablePanel:2947]</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;buildAttachmentConfig</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>构建附件配置区:固定/不固定双模式切换</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;buildAttachmentConfig:3010]</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_onGoNextStep</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>下一步点击:跳转负载配给页(本轮UI占位)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onGoNextStep:3001]</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>新增-占位</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_removeBodyVariable</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>删除正文光标处的变量(右侧面板入口)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_removeBodyVariable:3006]</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;onAddFolder</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>不固定附件添加文件夹(本轮UI占位)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;onAddFolder:3078]</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>新增-占位</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_wrapLayout1</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>layout&lt;QLayout&gt;</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>布局装入单Widget(供Section复用)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_wrapLayout1:2848]</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>新增-辅助</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_wrapInput</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>edit&lt;QWidget&gt;</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>单行输入框装入Widget(供Section复用)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_wrapInput:2855]</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>新增-辅助</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AdvancedPage-&gt;_wrapPlain</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>edit&lt;QWidget&gt;</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>编辑器装入Widget(供Section复用)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_wrapPlain:2863]</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:57:47</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>新增-辅助</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>_collectVariables</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>text&lt;str&gt;, source&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>将该来源文本中每个变量匹配逐条加入右侧变量列表(不去重)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>src/GUI/MainGUI.py[AdvancedPage-&gt;_collectVariables:3363]</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:20:37</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>配合去掉变量去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>_applyMarkHighlight</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>为含\/昵称单行框设置浅黄背景提示</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>src/GUI/MainGUI.py[AdvancedPage-&gt;_applyMarkHighlight:3371]</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:30:24</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>onAddFolder</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>选择附件文件夹并加入列表,存self.attach_folders供负载页使用</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>src/GUI/MainGUI.py[AdvancedPage-&gt;onAddFolder:3141]</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:30:24</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>新增,UI阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>MarkableLineEdit</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>text:文本</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>继承QLineEdit，在$$变量段自绘半透明浅黄背景实现局部高亮，无变量不变黄</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>src/GUI/MainGUI.py[MarkableLineEdit:2763]</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:39:35</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>新增类</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>_updateCorrelationTable</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>key: 无 参数: 无</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>刷新对应关系矩阵：行=收件人（含邮箱号），列=各标记位置，直观展示行对齐</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_updateCorrelationTable:3819]</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:05:42</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>新增邮箱号列；列序为 收件人/邮箱号/各标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>_readDataRows</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>list&amp;lt;str&amp;gt;</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>读取数据文件全部有效文本行，供对应关系矩阵使用；自动过滤空白行</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_readDataRows:3680]</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:44:43</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>CSV/TXT逐行过滤空行；Excel用openpyxl读第一工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>_collectMarkers</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>收集昵称/主题/正文全部变量标记（不含附件文件夹）</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_collectMarkers:3356]</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:44:43</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>附件文件夹由配置页单独配置，不计入负载标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>_buildRelationStep</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>构建第3步绑定关系与对应关系页（两个页签：绑定规则+对应关系展望）</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildRelationStep:3356]</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:05:42</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>从负载配给页拆出，避免UI拥挤</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>_setSearchBarVisible</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>visible&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>统一控制主窗口顶部搜索框与查询按钮的显示/隐藏</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;_setSearchBarVisible:715]</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:05:42</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>列表/模式页显示，发信页隐藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>_updateBindingTable</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>刷新绑定规则表：展示全部 标记→文件 绑定 + 追加「不固定附件」模式扫描到的附件表头行，未绑定标记以红色提示</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:57:18</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_updateBindingTable:3756]</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>_scanAttachmentFiles</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>list&lt;tuple&gt;</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>仅在不固定附件模式下扫描各文件夹内文件，构造 (folder_idx,file_name) 附件表头列表；按文件夹顺序+文件名字母序稳定对应</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:57:18</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_scanAttachmentFiles:3479]</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>_rebuildCorrOrderList</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>重建「列排序」可重排列表：默认先昵称/主题/正文标记后附件表头；InternalMove 拖拽排序；rowsMoved 信号触发矩阵刷新</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:57:18</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_rebuildCorrOrderList:3502]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>_colDisplayName</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>key&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>返回列键的显示名：标记键优先返回标记名，附件列回退为文件名</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:57:18</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_colDisplayName:3530]</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>_orderedColumnKeys</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>list&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>读取「列排序」列表当前的列键顺序（邮箱列固定不参与），供矩阵按用户排序列渲染</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:57:18</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_orderedColumnKeys:3542]</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>_scanFolderFiles</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>folder&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>扫描附件文件夹当前层文件，按文件名升序排列（不递归）</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_scanFolderFiles:3690]</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:11:27</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>第k收件人取各文件夹第k个文件，缺文件就跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>_naturalSortKey</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>name&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>自然排序key：数字段按int比较，使10排于2后</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_naturalSortKey:3690]</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:17:16</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>修复数字文件名字符串排序错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>_buildPreviewStep</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>构建第4步预览页：邮件列表+状态+继续生成按钮</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildPreviewStep:3435]</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>首进生成n=20封</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>_generateOneMail</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>row&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>按负载对齐规则生成第row封邮件完整内容</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_generateOneMail:3497]</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>第k收件人对齐第k行数据与附件</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>_replaceTemplate</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>text,src_name,row_values</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>按来源位置替换模板中的变量占位符</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_replaceTemplate:3541]</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>某来源第i个变量用key来源:i</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>_fillPreviewRows</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>start&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>分段生成并追加一批邮件到列表</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_fillPreviewRows:3576]</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>每批PREVIEW_BATCH_SIZE封</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>_initPreviewIfNeeded</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>首次进预览页时初始化总封数并生成第一批</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_initPreviewIfNeeded:3631]</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>切换页面不重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>_refreshPreviewRowFor</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>mail&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>保存后刷新列表对应行摘要</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_refreshPreviewRowFor:3615]</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PreviewMailDialog</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>parent,mail</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>QDialog</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>预览邮件详情查看/编辑对话框</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog:4490]</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-08-24 18:48:33</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>默认只读，编辑/保存/退出提醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BatchSendWorker</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>send_items,interval_candidates</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>QThread</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>后台批量发信线程：逐封发送并按随机间隔节流</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[BatchSendWorker:255]</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>0.2~0.5秒随机间隔防垃圾邮件判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>_buildSendStep</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>构建第5步发信页UI</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildSendStep:3269]</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>含发送状态表/汇总/重发失败按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>_buildSendItems</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>list&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>根据预览批次构造待发送项列表</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_buildSendItems:3333]</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>使用第4步编辑后的邮件内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>_resetSendTable</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>清空并重建发信列表</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_resetSendTable:3364]</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>进入发信页时填充</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>_updateSendSummary</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>刷新发信页底部汇总状态文本</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_updateSendSummary:3389]</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>_onStartBatchSend</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>点发送：弹提示、构建列表、启动批量发送(连接mail_started)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onStartBatchSend:3397]</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>开始发送弹提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>_onMailSentFinished</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>idx,success,msg</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>单封完成回调：更新状态/结果/发送时间及逐封重发按钮</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onMailSentFinished:3416]</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>记录发送时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>_onAllMailSent</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ok_cnt,fail_cnt</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>全部发送完成回调：提示并控制重发按钮</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onAllMailSent:3442]</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>_onRetryFailed</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>仅对失败邮件批量重发</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onRetryFailed:3460]</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>连接mail_started</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>_onRetryMailFinished</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>sub_idx,success,msg</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>重发单封完成：写回状态/结果/发送时间/重发按钮</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onRetryMailFinished:3490]</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>记录发送时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>_onRetryAllFinished</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>ok_cnt,fail_cnt</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>重发全部完成回调</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onRetryAllFinished:3518]</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:10:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>_setFooterSendState</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>sending&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>切换发信页底部发送按钮状态</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>切换发信页底部导航按钮状态：发送中禁用上一步与发送</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:13:13</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>发送中强制停留发信页</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>_isSending</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>判断当前是否处于批量发送中</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_isSending:3525]</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:13:13</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>发送中禁止切换步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>_senderHeader</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>tuple</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>构造发件人展示信息：优先用该封邮件配置页的发件人昵称(变量替换后)，回退from_edit与默认占位名</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_senderHeader:4876]</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:32:39</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>修复发件人昵称固定为默认的问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>_buildReadView</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>构建只读邮件视图：头部+HTML正文+附件</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_buildReadView:4885]</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>_refreshAttachLabel</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>刷新只读视图附件显示</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_refreshAttachLabel:4924]</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>_renderHtml</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>渲染HTML正文并注册内嵌图资源</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_renderHtml:4934]</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:27:14</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>resource key带cid前缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>_buildEditView</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>构建可编辑表单视图</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_buildEditView:4947]</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>_ensureSendTableBuilt</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>首次进入发信页构建发送列表，切换步骤不重建</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_ensureSendTableBuilt:3384]</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>状态持久化,不重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>_wrapRetryBtn</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>btn,enabled</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>QWidget</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>把逐封重发按钮装入居中容器</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_wrapRetryBtn:3427]</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>_getDisplayState</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>state&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>内部状态词转界面文案</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_getDisplayState:3438]</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>_setRowStatus</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>row,state,color</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>设置某行状态列文案颜色</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_setRowStatus:3453]</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>_setRowRetryEnabled</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>row,enabled</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>启用/禁用某行重发按钮</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_setRowRetryEnabled:3467]</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>_onRetryOne</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>单邮件的单独重发</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onRetryOne:3478]</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>_onMailStarted</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>某行邮件开始发送回调：置正在发送</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onMailStarted:3534]</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>_onRetryMailStarted</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sub_idx</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>重发某封开始发送回调</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_onRetryMailStarted:3616]</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>_reloadAttachList</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>刷新附件编辑列表(只显示文件名)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_reloadAttachList:5206]</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>_onPickAttachments</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>选择附件加入本封邮件</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_onPickAttachments:5212]</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>_onRemoveAttachment</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>移除选中的附件</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[PreviewMailDialog-&gt;_onRemoveAttachment:5227]</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>showCategoryData</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>mails&lt;list&lt;dict&gt;&gt;; tasks&lt;list&lt;dict&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>用独立邮件+任务文件夹混排填充分类视图</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;showCategoryData:1175]</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>showTaskDetail</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>task&lt;dict&gt;; mails&lt;list&lt;dict&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>进入某任务详情视图，标题显示任务名并仅列该任务邮件</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;showTaskDetail:1200]</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>_onBackTask</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>「返回列表」按钮：退出任务详情回到分类视图</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;_onBackTask:1215]</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>_renderRows</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>按 rows 渲染表格，区分邮件行与任务文件夹行</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;_renderRows:1226]</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>_splitRows</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>indices&lt;list&lt;int&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>tuple</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>把选中行号拆分为邮件id与任务id列表</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;_splitRows:1359]</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>_rowDisplayText</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>i&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>取某行的展示名（邮件主题/任务名）供删除确认提示</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MailListPage-&gt;_rowDisplayText:1384]</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>onRequestOpenTask</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>打开任务文件夹：草稿=恢复编辑，已发送/已删除=进入任务详情</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;onRequestOpenTask:764]</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>_showTaskDetail</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>进入任务详情视图：列出该任务下全部邮件</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;_showTaskDetail:780]</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>_restoreDraftTaskEditing</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>恢复草稿任务为高级模式可编辑状态，还原全部配置</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;_restoreDraftTaskEditing:794]</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>onRequestTaskDelete</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>task_ids&lt;list&lt;int&gt;&gt;; permanent&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>删除任务：常规移入已删除，彻底删除连带其下邮件物理删除</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;onRequestTaskDelete:811]</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>onRequestTaskRestore</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>恢复已删除任务回草稿箱（连带其下邮件）</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;onRequestTaskRestore:828]</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>onTaskListBack</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>任务详情「返回列表」：重建当前分类视图</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;onTaskListBack:836]</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>_cleanupExpiredTasks</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>清理已删除中保留超过30天的任务（连带其下邮件）</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;_cleanupExpiredTasks:841]</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>_syncLoadList</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>增量同步负载配给页：只增不减地并入配置页新增标记，保留既有绑定</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_syncLoadList:4691]</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:35:48</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>修复新增标记无法在负载页配给</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>_fillMarkerCombo</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>markers&lt;list&lt;tuple&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>按(key,name)填充标记下拉框并联动启用/禁用</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[AdvancedPage-&gt;_fillMarkerCombo:4722]</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:35:48</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>从_rebuildLoadList抽取复用</t>
         </is>
       </c>
     </row>
@@ -10586,7 +13923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11376,6 +14713,384 @@
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>insertTask</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>category&lt;str&gt;; name&lt;str&gt;; config&lt;dict|str&gt;; send_time&lt;str|None&gt;; mail_count&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>插入一条高级模式任务记录，返回任务id</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;insertTask:340]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>getTask</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>dict|None</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>按id查询单条任务，config解析为dict</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;getTask:362]</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>getTasks</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>category&lt;str|None&gt;</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>list&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>按分类查询任务列表，按时间倒序</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;getTasks:373]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>getMailsByTask</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>list&lt;dict&gt;</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>查询某任务下全部邮件</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;getMailsByTask:390]</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>updateTask</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;; **fields</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>更新任务记录指定字段</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;updateTask:403]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>moveTask</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;; new_category&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>移动任务到新分类并同步其下邮件分类</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;moveTask:429]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>deleteTask</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>task_id&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>物理删除任务及其下全部邮件</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;deleteTask:453]</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>countTasks</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>category&lt;str|None&gt;</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>统计任务数量，供默认任务名序号使用</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;countTasks:465]</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>_taskToDict</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>row&lt;sqlite3.Row&gt;</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>任务Row转dict，config解析为dict</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[MailDatabase-&gt;_taskToDict:478]</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:10:05</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>新增</t>
         </is>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -17,6 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="database" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_recipient_bulk" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_mail_query" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="option_settings" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logger" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cred_app" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_credentials" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1707,6 +1711,80 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>新增数量校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loadSmtpCredentials</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tuple&lt;str,str&gt;</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加载SMTP账号密码：优先经C扩展解密credentials.enc，失败回退config明文(修改)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(src/Email/MainEmail.py)[loadSmtpCredentials:58]</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>_decryptFromCredentialFile</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>enc_path&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tuple&lt;str,str&gt;|None</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>读取加密凭据文件并调cred_app.pyd解密，按账号\n密码拆分返回，失败返回None(新增)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(src/Email/MainEmail.py)[_decryptFromCredentialFile:99]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
         </is>
       </c>
     </row>
@@ -1815,6 +1893,799 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>函数名/方法名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SettingsManager</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SettingsManager 实例</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>设置项管理器：读取/修改/持久化用户可配置项</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager:27]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>从设置文件读取已保存配置并覆盖默认值</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager-&gt;load:52]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>key&lt;str&gt;, default&lt;any&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>获取指定设置项当前值</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager-&gt;get:70]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>key&lt;str&gt;, value&lt;any&gt;</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>修改指定设置项的内存值</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager-&gt;set:84]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>save</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>将当前设置持久化到 settings.json</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager-&gt;save:95]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>返回当前全部设置的副本</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[SettingsManager-&gt;all:108]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>getSettingsInstance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SettingsManager</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>获取全局唯一设置管理器单例</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(option/settings.py)[getSettingsInstance:121]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>函数名/方法名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>setupLogging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>level&lt;int&gt;</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>全局初始化日志系统：配置文件+控制台handler、按日期轮转</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(src/logger.py)[setupLogging:72]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>getLogger</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>name&lt;str|None&gt;</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>logging.Logger</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>获取模块专属logger实例</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(src/logger.py)[getLogger:120]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>isInitialized</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>检查日志系统是否已初始化</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(src/logger.py)[isInitialized:134]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>logException</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>logger&lt;Logger&gt;, msg&lt;str&gt;, exc_info&lt;bool&gt;</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>便捷方法：记录异常日志含完整堆栈</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(src/logger.py)[logException:142]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>_resolveLogPath</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>解析日志保存目录：优先从设置读取，失败回退默认路径</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(src/logger.py)[_resolveLogPath:55]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>函数名/方法名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>decrypt_credentials</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ciphertext&lt;bytes&gt;, key_part_b&lt;bytes&gt;</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C扩展对外解密函数：组综完整密钥(分片A+分片B+盐)后对密文做对称变换还原明文</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(src/security/cred_app.pyx)[decrypt_credentials:53]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>_mix</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>src&lt;const unsigned char*&gt;, dst&lt;unsigned char*&gt;, n&lt;Py_ssize_t&gt;, key&lt;const unsigned char*&gt;, keylen&lt;Py_ssize_t&gt;</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>纯C对称变换：字节流XOR+状态累积，加密/解密同函数(自反可逆)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(src/security/cred_app.pyx)[_mix:30]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>函数名/方法名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>返回值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>函数意义</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>记录/修改时间</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>读config明文凭据-&gt;对称变换加密-&gt;base64写credentials.enc，并回读解密校验</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(src/security/store_credentials.py)[main:72]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>buildFullKey</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bytes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>组装完整密钥=分片A+分片B+盐(顺序与C扩展一致)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(src/security/store_credentials.py)[buildFullKey:41]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>encryptTransform</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>data&lt;bytes&gt;, key&lt;bytes&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bytes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Python版对称变换(与C扩展_mix一致)：字节流XOR+状态累积，自反可逆</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(src/security/store_credentials.py)[encryptTransform:51]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20260825011404</t>
         </is>
       </c>
     </row>
@@ -2304,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I287"/>
+  <dimension ref="A1:I295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7272,7 +8143,6 @@
         </is>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -7611,7 +8481,6 @@
         </is>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -7654,7 +8523,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
@@ -7697,7 +8565,6 @@
         </is>
       </c>
     </row>
-    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -7735,7 +8602,6 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
@@ -7778,7 +8644,6 @@
         </is>
       </c>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -7821,7 +8686,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -7864,7 +8728,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
@@ -7907,7 +8770,6 @@
         </is>
       </c>
     </row>
-    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -7950,7 +8812,6 @@
         </is>
       </c>
     </row>
-    <row r="157"/>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
@@ -7988,7 +8849,6 @@
         </is>
       </c>
     </row>
-    <row r="159"/>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
@@ -8031,7 +8891,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -8074,7 +8933,6 @@
         </is>
       </c>
     </row>
-    <row r="163"/>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
@@ -8117,7 +8975,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
@@ -8160,7 +9017,6 @@
         </is>
       </c>
     </row>
-    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -8203,7 +9059,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
@@ -8246,7 +9101,6 @@
         </is>
       </c>
     </row>
-    <row r="171"/>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -8289,7 +9143,6 @@
         </is>
       </c>
     </row>
-    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
@@ -8332,7 +9185,6 @@
         </is>
       </c>
     </row>
-    <row r="175"/>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
@@ -8375,7 +9227,6 @@
         </is>
       </c>
     </row>
-    <row r="177"/>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
@@ -8418,7 +9269,6 @@
         </is>
       </c>
     </row>
-    <row r="179"/>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
@@ -12867,6 +13717,262 @@
       <c r="H287" t="inlineStr">
         <is>
           <t>从_rebuildLoadList抽取复用</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>refreshRuntimeDefaults</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>设置保存后刷新受设置影响的运行时默认昵称</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[refreshRuntimeDefaults:73]</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SettingsDialog</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>parent&lt;QWidget|None&gt;</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>应用设置页：铺满窗口编辑可修改设置项并保存</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog:479]</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>_buildUi</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>构建设置页布局（标题+返回+表单+保存）</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog-&gt;_buildUi:504]</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>_loadValues</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>把当前设置值回填到各控件</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog-&gt;_loadValues:562]</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>saveChanges</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>读界面输入写回设置落盘并刷新运行时默认值</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog-&gt;saveChanges:567]</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>goBack</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>关闭设置页返回主页</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog-&gt;goBack:579]</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>openSettings</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>打开铺满窗口的设置页（左下角齿轮入口触发）</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[MainWindow-&gt;openSettings:763]</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>_browseLogPath</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>打开目录选择框并把所选目录写入日志路径输入框</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>(src/GUI/MainGUI.py)[SettingsDialog-&gt;_browseLogPath:623]</t>
         </is>
       </c>
     </row>
@@ -13923,7 +15029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15093,6 +16199,132 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>_xorObfuscate</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>raw_bytes&lt;bytes&gt;</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>bytes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>按固定密钥逐字节异或做混淆（加解密对称）</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[_xorObfuscate:43]</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:31:36</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>任务配置脱敏用</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>encryptTaskConfig</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>obj&lt;dict|str&gt;</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>序列化并混淆任务配置，得到可安全落库的密文</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[encryptTaskConfig:55]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:31:36</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>config 落库加密</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>decryptTaskConfig</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cipher_text&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>解析数据库中任务配置（自动解密混淆，兼容旧明文）</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>(src/database/database.py)[decryptTaskConfig:71]</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:31:36</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>config 读库解密</t>
         </is>
       </c>
     </row>
@@ -15107,7 +16339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15834,6 +17066,38 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>_getDataFileEncoding</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>读取设置中配置的 CSV/TXT 收件人数据文件默认编码</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(src/activity/recipient_bulk.py)[_getDataFileEncoding:96]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logger" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cred_app" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_credentials" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="setup_crypt" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2694,6 +2695,104 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>selectSource</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tuple&lt;str,str&gt;</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>选择扩展源码：优先 .pyx（需 Cython），否则直接用 Cython 产出的 .c</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>(src/security/setup_crypt.py)[selectSource:24]</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:51:05</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>macOS 复用 .c 免装 Cython</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>buildExtensions</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>构建扩展模块列表；.pyx 走 cythonize、.c 直接编译，按平台设置编译参数</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(src/security/setup_crypt.py)[buildExtensions:35]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:51:05</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Windows 产 .pyd / macOS 产 .so，保证解密结果一致</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14930,12 +15029,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-23 15:01:25</t>
+          <t>2026-08-25 17:51:05</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>修正开发态=项目根</t>
+          <t>已适配 macOS：打包后用户数据放 ~/Library/Application Support/EmailHelper，Windows 仍为 exe 目录</t>
         </is>
       </c>
     </row>

--- a/ProjectDescription/FunctionNameReg.xlsx
+++ b/ProjectDescription/FunctionNameReg.xlsx
@@ -14774,7 +14774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(src/main.py)[main:20]</t>
+          <t>(src/main.py)[main:60]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-23 14:53:08</t>
+          <t>2026-08-28 12:49:37</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -14900,6 +14900,48 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>路径统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>createSplash</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>QSplashScreen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>程序化绘制启动闪屏(品牌色底+主标题+加载提示)，消除启动黑屏无反馈</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(src/main.py)[createSplash:27]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:49:37</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>新增：缓解双击后长时间无窗口的问题</t>
         </is>
       </c>
     </row>
